--- a/export/a_r_25/v3.xlsx
+++ b/export/a_r_25/v3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002C3E50"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -99,6 +109,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -585,8 +601,16 @@
           <t>2:00</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -629,9 +653,21 @@
           <t>7:25</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -674,9 +710,21 @@
           <t>7:00</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -719,9 +767,21 @@
           <t>7:30</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -764,9 +824,21 @@
           <t>7:15</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -814,8 +886,16 @@
           <t>2:00</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -858,9 +938,21 @@
           <t>7:10</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -903,9 +995,21 @@
           <t>7:25</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -948,9 +1052,21 @@
           <t>7:40</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -993,9 +1109,21 @@
           <t>7:45</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1043,8 +1171,16 @@
           <t>2:00</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1087,9 +1223,21 @@
           <t>7:30</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1132,9 +1280,21 @@
           <t>7:35</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1177,9 +1337,21 @@
           <t>7:05</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1222,9 +1394,21 @@
           <t>7:40</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1259,6 +1443,102 @@
       </c>
       <c r="K17" s="4" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ימים:</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ שעות:</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>114:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>100% שעות:</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>108:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>125% שעות:</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>6:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>150% שעות:</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>שבת 150%:</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>0:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>בונוס:</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>נסיעות:</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
